--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0161.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0161.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Đừng lo. {Male=Anh ấy;Female=Cô ấy} là khách của Bậc Thầy Chế Tạo Búp Bê mà.</t>
+          <t>Đừng lo. {Male=He;Female=She} là khách của Bậc Thầy Chế Tạo Búp Bê mà.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Thì sao hả!? Nó vẫn là con trai duy nhất của ta… Cậu biết gì chứ!?</t>
+          <t>Thì sao hả!? Nó vẫn là con trai duy nhất của tao… Cậu biết gì chứ!?</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Xin lỗi... Tớ không rành lắm về việc chăm sóc Cộng Hưởng Giả. Tớ cũng không giúp được gì nhiều hơn đâu.</t>
+          <t>Xin lỗi... Tớ không rành lắm về việc chăm sóc Resonator. Tớ cũng không giúp được gì nhiều hơn đâu.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Có lẽ cậu mới là người phù hợp làm Tuần Tra hơn ta.</t>
+          <t>Có lẽ cậu mới là người phù hợp làm Tuần Tra hơn tao.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Cậu cũng tử tế với lũ người kia và bọn bù nhìn của chúng nữa.</t>
+          <t>Mày cũng tử tế với lũ người kia và bọn bù nhìn của chúng nữa.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Sau chuyện này, ngươi phải nói thật với ta. Tất cả mọi thứ.</t>
+          <t>Sau chuyện này, mày phải nói thật với tao. Tất cả mọi thứ.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Này! Ngươi là thằng nào vậy? Buông {Male=hắn;Female=cô ta} ra ngay!</t>
+          <t>Này! Mày là thằng nào vậy? Buông {Male=him;Female=her} ra ngay!</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Nếu là ngươi, ta sẽ không dại dột làm gì đâu. Không thể để VIP của Kim Châu bị thương được, phải không?</t>
+          <t>Nếu là mày, tao sẽ không dại dột làm gì đâu. Không thể để VIP của Jinzhou bị thương được, phải không?</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Ối... Khỉ thật... Thôi được, để ta giao cho ngươi vậy.</t>
+          <t>Ối... Khỉ thật... Thôi được, để tao giao cho mày vậy.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Yes...</t>
+          <t>Ừ...</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Cậu đã làm gì vậy?!</t>
+          <t>Mày đã làm gì vậy?!</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Và sao cậu lại phải lo? Những {Male=thằng nhóc;Female=cô bé} thông minh thì biết giữ mồm giữ miệng của mình thôi.</t>
+          <t>Và sao cậu lại phải lo? Những {Male=boys;Female=girls} thông minh thì biết giữ mồm giữ miệng của mình thôi.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Giờ nếu không muốn gặp rắc rối, tốt nhất là làm theo lời ta... Ta sẽ giải thích sau.</t>
+          <t>Giờ nếu không muốn gặp rắc rối, tốt nhất là làm theo lời tao... Tao sẽ giải thích sau.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Đa số Cộng Hưởng Giả đó đều bị Overclocking ở nhiều mức độ khác nhau. Họ cần được chăm sóc khẩn cấp, các chuyên gia từ Học viện Huaxu đã có mặt rồi.</t>
+          <t>Đa số Resonator đó đều bị Overclocking ở nhiều mức độ khác nhau. Họ cần được chăm sóc khẩn cấp, các chuyên gia từ Học viện Huaxu đã có mặt rồi.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Vào khoảng thời gian đó, Dollmaker đã nghe ngóng về khả năng đặc biệt của cậu. Hắn bảo ta đưa cậu đến căn nhà an toàn đó.</t>
+          <t>Vào khoảng thời gian đó, Dollmaker đã nghe ngóng về khả năng đặc biệt của cậu. Hắn bảo tao đưa cậu đến căn nhà an toàn đó.</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Ta không nghĩ ta cần phải giúp đâu, vì ngươi tự lo được mà. Nhưng... nếu ngươi cần ta giúp, cứ nói nhé.</t>
+          <t>Tao không nghĩ tao cần phải giúp đâu, vì mày tự lo được mà. Nhưng... nếu mày cần tao giúp, cứ nói nhé.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Hắn nuôi ta lớn để biến ta thành Tuần Tra viên cho mục đích riêng. Hắn cần một gián điệp trong Cục An Ninh Công Cộng.</t>
+          <t>Hắn nuôi tao lớn để biến tao thành Tuần Tra viên cho mục đích riêng. Hắn cần một gián điệp trong Cục An Ninh Công Cộng.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Đừng có mà bảo cậu lại định rút lui vào lúc này chứ?</t>
+          <t>Đừng có mà bảo mày lại định rút lui vào lúc này chứ?</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Đây là khách của Bậc thầy Dollmaker. Cậu sẽ an toàn khi ở bên {Male=anh ấy;Female=cô ấy}.</t>
+          <t>Đây là khách của Bậc thầy Dollmaker. Cậu sẽ an toàn khi ở bên {Male=him;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Đủ rồi... Ngươi nghe rõ rồi đấy. Đứng yên đó, ta đi lấy đồ sơ cứu cho.</t>
+          <t>Đủ rồi... Mày nghe rõ rồi đấy. Đứng yên đó, tao đi lấy đồ sơ cứu cho.</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Mấy Tacet Discord làm ngươi bị thương à?</t>
+          <t>Mấy Tacet Discord làm mày bị thương à?</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Ta không biết... Nhưng chỗ này nghe có vẻ cực kỳ quan trọng với Sư phụ Thợ Gỗ. Ông ấy bảo ta phải bảo vệ nó bằng cả mạng sống.</t>
+          <t>Tao không biết... Nhưng chỗ này nghe có vẻ cực kỳ quan trọng với Sư phụ Thợ Gỗ. Ông ấy bảo tao phải bảo vệ nó bằng cả mạng sống.</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Cậu chắc muốn làm thế à? Ta nghĩ cậu sẽ hối hận đấy.</t>
+          <t>Cậu chắc muốn làm thế à? Tao nghĩ cậu sẽ hối hận đấy.</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Ủa? Vậy cậu đã đọc những gì viết bên trong rồi à?</t>
+          <t>Ủa? Vậy mày đã đọc những gì viết bên trong rồi à?</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Vâng, tôi có.</t>
+          <t>Ừ, ta có.</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Thử đếm số lượng xem. Ta có linh cảm mật mã là đấy. (4, 1, 2, 3)</t>
+          <t>Thử đếm số lượng xem. Tao có linh cảm mật mã là đấy. (4, 1, 2, 3)</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ta nghĩ mình đã để mất dấu chúng rồi...</t>
+          <t>Tao nghĩ mình đã để mất dấu chúng rồi...</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Haha, thôi đi, ta biết ngươi chịu được bao nhiêu đâu.</t>
+          <t>Haha, thôi đi, tao biết mày chịu được bao nhiêu đâu.</t>
         </is>
       </c>
     </row>
